--- a/selection_rod.xlsx
+++ b/selection_rod.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="163">
   <si>
     <t xml:space="preserve">CODE H</t>
   </si>
@@ -734,7 +734,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -863,62 +863,62 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -939,15 +939,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1227,6 +1219,27 @@
       <c r="H1" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="W1" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="AF1" s="1" t="n">
         <v>1</v>
       </c>
@@ -1257,6 +1270,9 @@
       <c r="AX1" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AZ1" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="BC1" s="1" t="n">
         <v>1</v>
       </c>
@@ -1266,116 +1282,55 @@
       <c r="BE1" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="BL1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BO1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN1" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="BG1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CM1" s="1"/>
+      <c r="CN1" s="1"/>
       <c r="DK1" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="DL1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DQ1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DR1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DS1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DT1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DU1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DV1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DW1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DX1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DY1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="DZ1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="EA1" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="DL1" s="1"/>
+      <c r="DM1" s="1"/>
+      <c r="DN1" s="1"/>
+      <c r="DO1" s="1"/>
+      <c r="DP1" s="1"/>
+      <c r="DQ1" s="1"/>
+      <c r="DR1" s="1"/>
+      <c r="DS1" s="1"/>
+      <c r="DT1" s="1"/>
+      <c r="DU1" s="1"/>
+      <c r="DV1" s="1"/>
+      <c r="DW1" s="1"/>
+      <c r="DX1" s="1"/>
+      <c r="DY1" s="1"/>
+      <c r="DZ1" s="1"/>
+      <c r="EA1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1823,18 +1778,22 @@
         <v>104</v>
       </c>
       <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
+      <c r="U3" s="31" t="s">
+        <v>104</v>
+      </c>
       <c r="V3" s="31"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="33"/>
+      <c r="W3" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="X3" s="32"/>
       <c r="Y3" s="28"/>
       <c r="Z3" s="28"/>
       <c r="AA3" s="28"/>
       <c r="AB3" s="28"/>
       <c r="AC3" s="28"/>
       <c r="AD3" s="28"/>
-      <c r="AE3" s="34"/>
-      <c r="AF3" s="35" t="n">
+      <c r="AE3" s="33"/>
+      <c r="AF3" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AG3" s="23" t="s">
@@ -1846,7 +1805,7 @@
       <c r="AI3" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="AJ3" s="36" t="n">
+      <c r="AJ3" s="35" t="n">
         <v>0</v>
       </c>
       <c r="AK3" s="23" t="s">
@@ -1864,7 +1823,7 @@
       <c r="AO3" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="AP3" s="37" t="n">
+      <c r="AP3" s="36" t="n">
         <v>4</v>
       </c>
       <c r="AQ3" s="23" t="n">
@@ -1873,10 +1832,10 @@
       <c r="AR3" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS3" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="39" t="s">
+      <c r="AS3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="38" t="s">
         <v>110</v>
       </c>
       <c r="AU3" s="23" t="s">
@@ -1891,10 +1850,12 @@
       <c r="AX3" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="AY3" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="AZ3" s="33"/>
+      <c r="AY3" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AZ3" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="BA3" s="41"/>
       <c r="BB3" s="28" t="s">
         <v>111</v>
@@ -1909,12 +1870,18 @@
         <v>111</v>
       </c>
       <c r="BF3" s="42"/>
-      <c r="BG3" s="43"/>
+      <c r="BG3" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="BH3" s="28"/>
-      <c r="BI3" s="44"/>
-      <c r="BJ3" s="43"/>
-      <c r="BK3" s="44"/>
-      <c r="BL3" s="43" t="s">
+      <c r="BI3" s="43"/>
+      <c r="BJ3" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="BK3" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL3" s="40" t="s">
         <v>112</v>
       </c>
       <c r="BM3" s="28"/>
@@ -1930,7 +1897,7 @@
       <c r="BQ3" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BR3" s="44"/>
+      <c r="BR3" s="43"/>
       <c r="BS3" s="28" t="s">
         <v>112</v>
       </c>
@@ -1947,13 +1914,13 @@
       <c r="BX3" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BY3" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="BZ3" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="CA3" s="37" t="s">
+      <c r="BY3" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="BZ3" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="CA3" s="36" t="s">
         <v>110</v>
       </c>
       <c r="CB3" s="41"/>
@@ -1974,8 +1941,8 @@
       </c>
       <c r="CH3" s="41"/>
       <c r="CI3" s="31"/>
-      <c r="CJ3" s="32"/>
-      <c r="CK3" s="37" t="s">
+      <c r="CJ3" s="45"/>
+      <c r="CK3" s="36" t="s">
         <v>113</v>
       </c>
       <c r="CL3" s="41"/>
@@ -1993,28 +1960,28 @@
       </c>
       <c r="CQ3" s="41"/>
       <c r="CR3" s="31"/>
-      <c r="CS3" s="32"/>
-      <c r="CT3" s="37" t="s">
+      <c r="CS3" s="45"/>
+      <c r="CT3" s="36" t="s">
         <v>104</v>
       </c>
       <c r="CU3" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="CV3" s="38" t="n">
+      <c r="CV3" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="CW3" s="37"/>
+      <c r="CW3" s="36"/>
       <c r="CX3" s="23"/>
       <c r="CY3" s="23"/>
-      <c r="CZ3" s="38"/>
-      <c r="DA3" s="37"/>
+      <c r="CZ3" s="37"/>
+      <c r="DA3" s="36"/>
       <c r="DB3" s="23"/>
-      <c r="DC3" s="38"/>
-      <c r="DD3" s="39"/>
+      <c r="DC3" s="37"/>
+      <c r="DD3" s="38"/>
       <c r="DE3" s="23"/>
       <c r="DF3" s="23"/>
-      <c r="DG3" s="40"/>
-      <c r="DH3" s="33" t="n">
+      <c r="DG3" s="39"/>
+      <c r="DH3" s="32" t="n">
         <v>129</v>
       </c>
       <c r="DI3" s="28"/>
@@ -2137,14 +2104,14 @@
       <c r="W4" s="49" t="n">
         <v>0.8</v>
       </c>
-      <c r="X4" s="33"/>
+      <c r="X4" s="32"/>
       <c r="Y4" s="28"/>
       <c r="Z4" s="28"/>
       <c r="AA4" s="28"/>
       <c r="AB4" s="28"/>
       <c r="AC4" s="28"/>
       <c r="AD4" s="28"/>
-      <c r="AE4" s="34"/>
+      <c r="AE4" s="33"/>
       <c r="AF4" s="50" t="n">
         <v>0</v>
       </c>
@@ -2157,7 +2124,7 @@
       <c r="AI4" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="AJ4" s="36" t="n">
+      <c r="AJ4" s="35" t="n">
         <v>0</v>
       </c>
       <c r="AK4" s="23" t="s">
@@ -2175,7 +2142,7 @@
       <c r="AO4" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="AP4" s="37" t="n">
+      <c r="AP4" s="36" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" s="23" t="n">
@@ -2184,10 +2151,10 @@
       <c r="AR4" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS4" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="39" t="s">
+      <c r="AS4" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="38" t="s">
         <v>113</v>
       </c>
       <c r="AU4" s="23" t="s">
@@ -2202,13 +2169,13 @@
       <c r="AX4" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="AY4" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="AZ4" s="51" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BA4" s="52"/>
+      <c r="AY4" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AZ4" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="BA4" s="51"/>
       <c r="BB4" s="28" t="s">
         <v>111</v>
       </c>
@@ -2222,18 +2189,18 @@
         <v>111</v>
       </c>
       <c r="BF4" s="42"/>
-      <c r="BG4" s="53" t="n">
-        <v>0.4</v>
+      <c r="BG4" s="40" t="n">
+        <v>40</v>
       </c>
       <c r="BH4" s="47"/>
       <c r="BI4" s="49"/>
-      <c r="BJ4" s="53" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BK4" s="49" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL4" s="43" t="s">
+      <c r="BJ4" s="40" t="n">
+        <v>60</v>
+      </c>
+      <c r="BK4" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="BL4" s="40" t="s">
         <v>112</v>
       </c>
       <c r="BM4" s="28"/>
@@ -2249,7 +2216,7 @@
       <c r="BQ4" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BR4" s="44"/>
+      <c r="BR4" s="43"/>
       <c r="BS4" s="28" t="s">
         <v>112</v>
       </c>
@@ -2260,11 +2227,11 @@
       <c r="BV4" s="28"/>
       <c r="BW4" s="28"/>
       <c r="BX4" s="28"/>
-      <c r="BY4" s="34"/>
-      <c r="BZ4" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="CA4" s="37" t="s">
+      <c r="BY4" s="33"/>
+      <c r="BZ4" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="CA4" s="36" t="s">
         <v>110</v>
       </c>
       <c r="CB4" s="41"/>
@@ -2287,8 +2254,8 @@
       <c r="CI4" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="CJ4" s="38"/>
-      <c r="CK4" s="37" t="s">
+      <c r="CJ4" s="37"/>
+      <c r="CK4" s="36" t="s">
         <v>113</v>
       </c>
       <c r="CL4" s="41"/>
@@ -2308,30 +2275,30 @@
       <c r="CR4" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="CS4" s="38"/>
-      <c r="CT4" s="37" t="s">
+      <c r="CS4" s="37"/>
+      <c r="CT4" s="36" t="s">
         <v>104</v>
       </c>
       <c r="CU4" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="CV4" s="38" t="n">
+      <c r="CV4" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="CW4" s="37"/>
+      <c r="CW4" s="36"/>
       <c r="CX4" s="23"/>
       <c r="CY4" s="23"/>
-      <c r="CZ4" s="38"/>
-      <c r="DA4" s="37" t="n">
+      <c r="CZ4" s="37"/>
+      <c r="DA4" s="36" t="n">
         <v>100</v>
       </c>
       <c r="DB4" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="DC4" s="38" t="n">
+      <c r="DC4" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="DD4" s="39" t="s">
+      <c r="DD4" s="38" t="s">
         <v>110</v>
       </c>
       <c r="DE4" s="23" t="s">
@@ -2340,10 +2307,10 @@
       <c r="DF4" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="DG4" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="DH4" s="33" t="n">
+      <c r="DG4" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="DH4" s="32" t="n">
         <v>97</v>
       </c>
       <c r="DI4" s="28" t="s">
@@ -2470,15 +2437,15 @@
       <c r="W5" s="49" t="n">
         <v>0.98</v>
       </c>
-      <c r="X5" s="33"/>
+      <c r="X5" s="32"/>
       <c r="Y5" s="28"/>
       <c r="Z5" s="28"/>
       <c r="AA5" s="28"/>
       <c r="AB5" s="28"/>
       <c r="AC5" s="28"/>
       <c r="AD5" s="28"/>
-      <c r="AE5" s="34"/>
-      <c r="AF5" s="35" t="n">
+      <c r="AE5" s="33"/>
+      <c r="AF5" s="34" t="n">
         <v>1</v>
       </c>
       <c r="AG5" s="23" t="s">
@@ -2490,7 +2457,7 @@
       <c r="AI5" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="AJ5" s="36" t="n">
+      <c r="AJ5" s="35" t="n">
         <v>1</v>
       </c>
       <c r="AK5" s="23" t="s">
@@ -2508,7 +2475,7 @@
       <c r="AO5" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="AP5" s="37" t="n">
+      <c r="AP5" s="36" t="n">
         <v>1</v>
       </c>
       <c r="AQ5" s="23" t="n">
@@ -2517,10 +2484,10 @@
       <c r="AR5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS5" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" s="39" t="s">
+      <c r="AS5" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="38" t="s">
         <v>113</v>
       </c>
       <c r="AU5" s="23" t="s">
@@ -2535,10 +2502,10 @@
       <c r="AX5" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="AY5" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="AZ5" s="33" t="n">
+      <c r="AY5" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AZ5" s="32" t="n">
         <v>80</v>
       </c>
       <c r="BA5" s="41"/>
@@ -2555,18 +2522,18 @@
         <v>112</v>
       </c>
       <c r="BF5" s="42"/>
-      <c r="BG5" s="43" t="n">
+      <c r="BG5" s="40" t="n">
         <v>20</v>
       </c>
       <c r="BH5" s="28"/>
-      <c r="BI5" s="44"/>
-      <c r="BJ5" s="43" t="n">
+      <c r="BI5" s="43"/>
+      <c r="BJ5" s="40" t="n">
         <v>70</v>
       </c>
-      <c r="BK5" s="44" t="n">
+      <c r="BK5" s="43" t="n">
         <v>30</v>
       </c>
-      <c r="BL5" s="43" t="s">
+      <c r="BL5" s="40" t="s">
         <v>112</v>
       </c>
       <c r="BM5" s="28" t="s">
@@ -2584,7 +2551,7 @@
       <c r="BQ5" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BR5" s="44"/>
+      <c r="BR5" s="43"/>
       <c r="BS5" s="28" t="s">
         <v>112</v>
       </c>
@@ -2595,13 +2562,13 @@
       <c r="BV5" s="28"/>
       <c r="BW5" s="28"/>
       <c r="BX5" s="28"/>
-      <c r="BY5" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="BZ5" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="CA5" s="37" t="s">
+      <c r="BY5" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="BZ5" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="CA5" s="36" t="s">
         <v>110</v>
       </c>
       <c r="CB5" s="41"/>
@@ -2624,8 +2591,8 @@
       <c r="CI5" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="CJ5" s="38"/>
-      <c r="CK5" s="37" t="s">
+      <c r="CJ5" s="37"/>
+      <c r="CK5" s="36" t="s">
         <v>110</v>
       </c>
       <c r="CL5" s="41"/>
@@ -2645,24 +2612,24 @@
       <c r="CR5" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="CS5" s="38"/>
-      <c r="CT5" s="37" t="s">
+      <c r="CS5" s="37"/>
+      <c r="CT5" s="36" t="s">
         <v>104</v>
       </c>
       <c r="CU5" s="23"/>
-      <c r="CV5" s="38"/>
-      <c r="CW5" s="37"/>
+      <c r="CV5" s="37"/>
+      <c r="CW5" s="36"/>
       <c r="CX5" s="23"/>
       <c r="CY5" s="23"/>
-      <c r="CZ5" s="38"/>
-      <c r="DA5" s="37"/>
+      <c r="CZ5" s="37"/>
+      <c r="DA5" s="36"/>
       <c r="DB5" s="23"/>
-      <c r="DC5" s="38"/>
-      <c r="DD5" s="39"/>
+      <c r="DC5" s="37"/>
+      <c r="DD5" s="38"/>
       <c r="DE5" s="23"/>
       <c r="DF5" s="23"/>
-      <c r="DG5" s="40"/>
-      <c r="DH5" s="33" t="n">
+      <c r="DG5" s="39"/>
+      <c r="DH5" s="32" t="n">
         <v>309</v>
       </c>
       <c r="DI5" s="28" t="s">
@@ -2750,18 +2717,22 @@
         <v>104</v>
       </c>
       <c r="T6" s="31"/>
-      <c r="U6" s="31"/>
+      <c r="U6" s="31" t="s">
+        <v>104</v>
+      </c>
       <c r="V6" s="31"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="33"/>
+      <c r="W6" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="X6" s="32"/>
       <c r="Y6" s="28"/>
       <c r="Z6" s="28"/>
       <c r="AA6" s="28"/>
       <c r="AB6" s="28"/>
       <c r="AC6" s="28"/>
       <c r="AD6" s="28"/>
-      <c r="AE6" s="34"/>
-      <c r="AF6" s="35" t="n">
+      <c r="AE6" s="33"/>
+      <c r="AF6" s="34" t="n">
         <v>1</v>
       </c>
       <c r="AG6" s="23" t="s">
@@ -2773,7 +2744,7 @@
       <c r="AI6" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="AJ6" s="36" t="n">
+      <c r="AJ6" s="35" t="n">
         <v>1</v>
       </c>
       <c r="AK6" s="23" t="s">
@@ -2791,7 +2762,7 @@
       <c r="AO6" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="AP6" s="37" t="n">
+      <c r="AP6" s="36" t="n">
         <v>3</v>
       </c>
       <c r="AQ6" s="23" t="n">
@@ -2800,10 +2771,10 @@
       <c r="AR6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS6" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT6" s="39" t="s">
+      <c r="AS6" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="38" t="s">
         <v>113</v>
       </c>
       <c r="AU6" s="23" t="s">
@@ -2818,10 +2789,12 @@
       <c r="AX6" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="AY6" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="AZ6" s="33"/>
+      <c r="AY6" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AZ6" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="BA6" s="41"/>
       <c r="BB6" s="28" t="s">
         <v>111</v>
@@ -2836,12 +2809,18 @@
         <v>112</v>
       </c>
       <c r="BF6" s="42"/>
-      <c r="BG6" s="43"/>
+      <c r="BG6" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="BH6" s="28"/>
-      <c r="BI6" s="44"/>
-      <c r="BJ6" s="43"/>
-      <c r="BK6" s="44"/>
-      <c r="BL6" s="43" t="s">
+      <c r="BI6" s="43"/>
+      <c r="BJ6" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="BK6" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL6" s="40" t="s">
         <v>112</v>
       </c>
       <c r="BM6" s="28" t="s">
@@ -2855,10 +2834,10 @@
         <v>112</v>
       </c>
       <c r="BQ6" s="28"/>
-      <c r="BR6" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="BS6" s="33" t="s">
+      <c r="BR6" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="BS6" s="32" t="s">
         <v>112</v>
       </c>
       <c r="BT6" s="28" t="s">
@@ -2876,13 +2855,13 @@
       <c r="BX6" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BY6" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="BZ6" s="45" t="s">
-        <v>113</v>
-      </c>
-      <c r="CA6" s="37" t="s">
+      <c r="BY6" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="BZ6" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="CA6" s="36" t="s">
         <v>113</v>
       </c>
       <c r="CB6" s="41"/>
@@ -2905,8 +2884,8 @@
       <c r="CI6" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="CJ6" s="38"/>
-      <c r="CK6" s="37" t="s">
+      <c r="CJ6" s="37"/>
+      <c r="CK6" s="36" t="s">
         <v>110</v>
       </c>
       <c r="CL6" s="41"/>
@@ -2926,24 +2905,24 @@
       <c r="CR6" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="CS6" s="38"/>
-      <c r="CT6" s="37" t="s">
+      <c r="CS6" s="37"/>
+      <c r="CT6" s="36" t="s">
         <v>104</v>
       </c>
       <c r="CU6" s="23"/>
-      <c r="CV6" s="38"/>
-      <c r="CW6" s="37"/>
+      <c r="CV6" s="37"/>
+      <c r="CW6" s="36"/>
       <c r="CX6" s="23"/>
       <c r="CY6" s="23"/>
-      <c r="CZ6" s="38"/>
-      <c r="DA6" s="37"/>
+      <c r="CZ6" s="37"/>
+      <c r="DA6" s="36"/>
       <c r="DB6" s="23"/>
-      <c r="DC6" s="38"/>
-      <c r="DD6" s="39"/>
+      <c r="DC6" s="37"/>
+      <c r="DD6" s="38"/>
       <c r="DE6" s="23"/>
       <c r="DF6" s="23"/>
-      <c r="DG6" s="40"/>
-      <c r="DH6" s="33" t="n">
+      <c r="DG6" s="39"/>
+      <c r="DH6" s="32" t="n">
         <v>572</v>
       </c>
       <c r="DI6" s="28"/>
@@ -3055,18 +3034,22 @@
         <v>104</v>
       </c>
       <c r="T7" s="31"/>
-      <c r="U7" s="31"/>
+      <c r="U7" s="31" t="s">
+        <v>104</v>
+      </c>
       <c r="V7" s="31"/>
-      <c r="W7" s="32"/>
-      <c r="X7" s="33"/>
+      <c r="W7" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="X7" s="32"/>
       <c r="Y7" s="28"/>
       <c r="Z7" s="28"/>
       <c r="AA7" s="28"/>
       <c r="AB7" s="28"/>
       <c r="AC7" s="28"/>
       <c r="AD7" s="28"/>
-      <c r="AE7" s="34"/>
-      <c r="AF7" s="35" t="n">
+      <c r="AE7" s="33"/>
+      <c r="AF7" s="34" t="n">
         <v>1</v>
       </c>
       <c r="AG7" s="23" t="s">
@@ -3078,7 +3061,7 @@
       <c r="AI7" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="AJ7" s="36" t="n">
+      <c r="AJ7" s="35" t="n">
         <v>3</v>
       </c>
       <c r="AK7" s="23" t="s">
@@ -3096,7 +3079,7 @@
       <c r="AO7" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="AP7" s="37" t="n">
+      <c r="AP7" s="36" t="n">
         <v>36</v>
       </c>
       <c r="AQ7" s="23" t="n">
@@ -3105,10 +3088,10 @@
       <c r="AR7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS7" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT7" s="39" t="s">
+      <c r="AS7" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" s="38" t="s">
         <v>113</v>
       </c>
       <c r="AU7" s="23" t="s">
@@ -3123,10 +3106,12 @@
       <c r="AX7" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="AY7" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="AZ7" s="33"/>
+      <c r="AY7" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AZ7" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="BA7" s="41"/>
       <c r="BB7" s="28" t="s">
         <v>111</v>
@@ -3141,12 +3126,18 @@
         <v>112</v>
       </c>
       <c r="BF7" s="42"/>
-      <c r="BG7" s="43"/>
+      <c r="BG7" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="BH7" s="28"/>
-      <c r="BI7" s="44"/>
-      <c r="BJ7" s="43"/>
-      <c r="BK7" s="44"/>
-      <c r="BL7" s="43" t="s">
+      <c r="BI7" s="43"/>
+      <c r="BJ7" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="BK7" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL7" s="40" t="s">
         <v>112</v>
       </c>
       <c r="BM7" s="28"/>
@@ -3162,10 +3153,10 @@
       <c r="BQ7" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BR7" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="BS7" s="33" t="s">
+      <c r="BR7" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="BS7" s="32" t="s">
         <v>112</v>
       </c>
       <c r="BT7" s="28" t="s">
@@ -3183,13 +3174,13 @@
       <c r="BX7" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BY7" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="BZ7" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="CA7" s="37" t="s">
+      <c r="BY7" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="BZ7" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="CA7" s="36" t="s">
         <v>110</v>
       </c>
       <c r="CB7" s="41"/>
@@ -3210,8 +3201,8 @@
       </c>
       <c r="CH7" s="41"/>
       <c r="CI7" s="31"/>
-      <c r="CJ7" s="32"/>
-      <c r="CK7" s="37" t="s">
+      <c r="CJ7" s="45"/>
+      <c r="CK7" s="36" t="s">
         <v>113</v>
       </c>
       <c r="CL7" s="41"/>
@@ -3229,24 +3220,24 @@
       </c>
       <c r="CQ7" s="41"/>
       <c r="CR7" s="31"/>
-      <c r="CS7" s="32"/>
-      <c r="CT7" s="37" t="s">
+      <c r="CS7" s="45"/>
+      <c r="CT7" s="36" t="s">
         <v>104</v>
       </c>
       <c r="CU7" s="23"/>
-      <c r="CV7" s="38"/>
-      <c r="CW7" s="37"/>
+      <c r="CV7" s="37"/>
+      <c r="CW7" s="36"/>
       <c r="CX7" s="23"/>
       <c r="CY7" s="23"/>
-      <c r="CZ7" s="38"/>
-      <c r="DA7" s="37"/>
+      <c r="CZ7" s="37"/>
+      <c r="DA7" s="36"/>
       <c r="DB7" s="23"/>
-      <c r="DC7" s="38"/>
-      <c r="DD7" s="39"/>
+      <c r="DC7" s="37"/>
+      <c r="DD7" s="38"/>
       <c r="DE7" s="23"/>
       <c r="DF7" s="23"/>
-      <c r="DG7" s="40"/>
-      <c r="DH7" s="33" t="n">
+      <c r="DG7" s="39"/>
+      <c r="DH7" s="32" t="n">
         <v>764</v>
       </c>
       <c r="DI7" s="28"/>
@@ -3358,18 +3349,22 @@
         <v>104</v>
       </c>
       <c r="T8" s="31"/>
-      <c r="U8" s="31"/>
+      <c r="U8" s="31" t="s">
+        <v>104</v>
+      </c>
       <c r="V8" s="31"/>
-      <c r="W8" s="32"/>
-      <c r="X8" s="33"/>
+      <c r="W8" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="X8" s="32"/>
       <c r="Y8" s="28"/>
       <c r="Z8" s="28"/>
       <c r="AA8" s="28"/>
       <c r="AB8" s="28"/>
       <c r="AC8" s="28"/>
       <c r="AD8" s="28"/>
-      <c r="AE8" s="34"/>
-      <c r="AF8" s="35" t="n">
+      <c r="AE8" s="33"/>
+      <c r="AF8" s="34" t="n">
         <v>0</v>
       </c>
       <c r="AG8" s="23" t="s">
@@ -3381,7 +3376,7 @@
       <c r="AI8" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="AJ8" s="36" t="n">
+      <c r="AJ8" s="35" t="n">
         <v>1</v>
       </c>
       <c r="AK8" s="23" t="s">
@@ -3399,7 +3394,7 @@
       <c r="AO8" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="AP8" s="37" t="n">
+      <c r="AP8" s="36" t="n">
         <v>1</v>
       </c>
       <c r="AQ8" s="23" t="n">
@@ -3408,10 +3403,10 @@
       <c r="AR8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS8" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" s="39" t="s">
+      <c r="AS8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="38" t="s">
         <v>110</v>
       </c>
       <c r="AU8" s="23" t="s">
@@ -3426,10 +3421,12 @@
       <c r="AX8" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="AY8" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="AZ8" s="33"/>
+      <c r="AY8" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AZ8" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="BA8" s="41"/>
       <c r="BB8" s="28" t="s">
         <v>111</v>
@@ -3444,12 +3441,18 @@
         <v>111</v>
       </c>
       <c r="BF8" s="42"/>
-      <c r="BG8" s="43"/>
+      <c r="BG8" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="BH8" s="28"/>
-      <c r="BI8" s="44"/>
-      <c r="BJ8" s="43"/>
-      <c r="BK8" s="44"/>
-      <c r="BL8" s="43" t="s">
+      <c r="BI8" s="43"/>
+      <c r="BJ8" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="BK8" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL8" s="40" t="s">
         <v>112</v>
       </c>
       <c r="BM8" s="28" t="s">
@@ -3467,10 +3470,10 @@
       <c r="BQ8" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BR8" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="BS8" s="33" t="s">
+      <c r="BR8" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="BS8" s="32" t="s">
         <v>112</v>
       </c>
       <c r="BT8" s="28" t="s">
@@ -3486,13 +3489,13 @@
       <c r="BX8" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BY8" s="34" t="s">
-        <v>112</v>
-      </c>
-      <c r="BZ8" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="CA8" s="37" t="s">
+      <c r="BY8" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="BZ8" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="CA8" s="36" t="s">
         <v>110</v>
       </c>
       <c r="CB8" s="41"/>
@@ -3515,8 +3518,8 @@
       <c r="CI8" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="CJ8" s="38"/>
-      <c r="CK8" s="37" t="s">
+      <c r="CJ8" s="37"/>
+      <c r="CK8" s="36" t="s">
         <v>113</v>
       </c>
       <c r="CL8" s="41"/>
@@ -3536,24 +3539,24 @@
       <c r="CR8" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="CS8" s="38"/>
-      <c r="CT8" s="37" t="s">
+      <c r="CS8" s="37"/>
+      <c r="CT8" s="36" t="s">
         <v>104</v>
       </c>
       <c r="CU8" s="23"/>
-      <c r="CV8" s="38"/>
-      <c r="CW8" s="37"/>
+      <c r="CV8" s="37"/>
+      <c r="CW8" s="36"/>
       <c r="CX8" s="23"/>
       <c r="CY8" s="23"/>
-      <c r="CZ8" s="38"/>
-      <c r="DA8" s="37"/>
+      <c r="CZ8" s="37"/>
+      <c r="DA8" s="36"/>
       <c r="DB8" s="23"/>
-      <c r="DC8" s="38"/>
-      <c r="DD8" s="39"/>
+      <c r="DC8" s="37"/>
+      <c r="DD8" s="38"/>
       <c r="DE8" s="23"/>
       <c r="DF8" s="23"/>
-      <c r="DG8" s="40"/>
-      <c r="DH8" s="33" t="n">
+      <c r="DG8" s="39"/>
+      <c r="DH8" s="32" t="n">
         <v>305</v>
       </c>
       <c r="DI8" s="28"/>
@@ -3665,18 +3668,22 @@
         <v>104</v>
       </c>
       <c r="T9" s="31"/>
-      <c r="U9" s="31"/>
+      <c r="U9" s="31" t="s">
+        <v>104</v>
+      </c>
       <c r="V9" s="31"/>
-      <c r="W9" s="32"/>
-      <c r="X9" s="33"/>
+      <c r="W9" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="X9" s="32"/>
       <c r="Y9" s="28"/>
       <c r="Z9" s="28"/>
       <c r="AA9" s="28"/>
       <c r="AB9" s="28"/>
       <c r="AC9" s="28"/>
       <c r="AD9" s="28"/>
-      <c r="AE9" s="34"/>
-      <c r="AF9" s="35" t="n">
+      <c r="AE9" s="33"/>
+      <c r="AF9" s="34" t="n">
         <v>1</v>
       </c>
       <c r="AG9" s="23" t="s">
@@ -3688,7 +3695,7 @@
       <c r="AI9" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="AJ9" s="36" t="n">
+      <c r="AJ9" s="35" t="n">
         <v>2</v>
       </c>
       <c r="AK9" s="23" t="s">
@@ -3706,7 +3713,7 @@
       <c r="AO9" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="AP9" s="37" t="n">
+      <c r="AP9" s="36" t="n">
         <v>13</v>
       </c>
       <c r="AQ9" s="23" t="n">
@@ -3715,10 +3722,10 @@
       <c r="AR9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS9" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT9" s="39" t="s">
+      <c r="AS9" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="38" t="s">
         <v>110</v>
       </c>
       <c r="AU9" s="23" t="s">
@@ -3733,10 +3740,12 @@
       <c r="AX9" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="AY9" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="AZ9" s="33"/>
+      <c r="AY9" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="AZ9" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="BA9" s="41"/>
       <c r="BB9" s="28" t="s">
         <v>111</v>
@@ -3751,12 +3760,18 @@
         <v>111</v>
       </c>
       <c r="BF9" s="42"/>
-      <c r="BG9" s="43"/>
+      <c r="BG9" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="BH9" s="28"/>
-      <c r="BI9" s="44"/>
-      <c r="BJ9" s="43"/>
-      <c r="BK9" s="44"/>
-      <c r="BL9" s="43" t="s">
+      <c r="BI9" s="43"/>
+      <c r="BJ9" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="BK9" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="BL9" s="40" t="s">
         <v>112</v>
       </c>
       <c r="BM9" s="28" t="s">
@@ -3774,8 +3789,8 @@
       <c r="BQ9" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BR9" s="44"/>
-      <c r="BS9" s="33" t="s">
+      <c r="BR9" s="43"/>
+      <c r="BS9" s="32" t="s">
         <v>112</v>
       </c>
       <c r="BT9" s="28" t="s">
@@ -3787,11 +3802,11 @@
       <c r="BX9" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="BY9" s="34"/>
-      <c r="BZ9" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="CA9" s="37" t="s">
+      <c r="BY9" s="33"/>
+      <c r="BZ9" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="CA9" s="36" t="s">
         <v>110</v>
       </c>
       <c r="CB9" s="41"/>
@@ -3814,8 +3829,8 @@
       <c r="CI9" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="CJ9" s="38"/>
-      <c r="CK9" s="37" t="s">
+      <c r="CJ9" s="37"/>
+      <c r="CK9" s="36" t="s">
         <v>113</v>
       </c>
       <c r="CL9" s="41"/>
@@ -3835,24 +3850,24 @@
       <c r="CR9" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="CS9" s="38"/>
-      <c r="CT9" s="37" t="s">
+      <c r="CS9" s="37"/>
+      <c r="CT9" s="36" t="s">
         <v>104</v>
       </c>
       <c r="CU9" s="23"/>
-      <c r="CV9" s="38"/>
-      <c r="CW9" s="37"/>
+      <c r="CV9" s="37"/>
+      <c r="CW9" s="36"/>
       <c r="CX9" s="23"/>
       <c r="CY9" s="23"/>
-      <c r="CZ9" s="38"/>
-      <c r="DA9" s="37"/>
+      <c r="CZ9" s="37"/>
+      <c r="DA9" s="36"/>
       <c r="DB9" s="23"/>
-      <c r="DC9" s="38"/>
-      <c r="DD9" s="39"/>
+      <c r="DC9" s="37"/>
+      <c r="DD9" s="38"/>
       <c r="DE9" s="23"/>
       <c r="DF9" s="23"/>
-      <c r="DG9" s="40"/>
-      <c r="DH9" s="33" t="n">
+      <c r="DG9" s="39"/>
+      <c r="DH9" s="32" t="n">
         <v>191</v>
       </c>
       <c r="DI9" s="28"/>
